--- a/input/dataset_maestro_semanal.xlsx
+++ b/input/dataset_maestro_semanal.xlsx
@@ -21,13 +21,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -422,94 +434,94 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>semana_inicio</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ventas_importe_real_2026_05</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ventas_registros</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ventas_cantidad_total</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>compras_importe_semanal</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>eventos_festivos_semana</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eventos_pago_semana</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>nacimientos_indice_semanal</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>inpc_observado_semana</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>temperatura_observada_semana</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dias_observados</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mes</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>trimestre</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>semana_anio</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>es_san_valentin</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>es_dia_nino</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>es_dia_madre</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="B2" t="n">
@@ -562,7 +574,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44571</v>
       </c>
       <c r="B3" t="n">
@@ -615,7 +627,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44578</v>
       </c>
       <c r="B4" t="n">
@@ -668,7 +680,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44585</v>
       </c>
       <c r="B5" t="n">
@@ -721,7 +733,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B6" t="n">
@@ -774,7 +786,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="B7" t="n">
@@ -827,7 +839,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44606</v>
       </c>
       <c r="B8" t="n">
@@ -880,7 +892,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44613</v>
       </c>
       <c r="B9" t="n">
@@ -933,7 +945,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B10" t="n">
@@ -986,7 +998,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44627</v>
       </c>
       <c r="B11" t="n">
@@ -1039,7 +1051,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44634</v>
       </c>
       <c r="B12" t="n">
@@ -1092,7 +1104,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44641</v>
       </c>
       <c r="B13" t="n">
@@ -1145,7 +1157,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44648</v>
       </c>
       <c r="B14" t="n">
@@ -1198,7 +1210,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44655</v>
       </c>
       <c r="B15" t="n">
@@ -1251,7 +1263,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44662</v>
       </c>
       <c r="B16" t="n">
@@ -1304,7 +1316,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44669</v>
       </c>
       <c r="B17" t="n">
@@ -1357,7 +1369,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44676</v>
       </c>
       <c r="B18" t="n">
@@ -1410,7 +1422,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44683</v>
       </c>
       <c r="B19" t="n">
@@ -1463,7 +1475,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="B20" t="n">
@@ -1516,7 +1528,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44697</v>
       </c>
       <c r="B21" t="n">
@@ -1569,7 +1581,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44704</v>
       </c>
       <c r="B22" t="n">
@@ -1622,7 +1634,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44711</v>
       </c>
       <c r="B23" t="n">
@@ -1675,7 +1687,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44718</v>
       </c>
       <c r="B24" t="n">
@@ -1728,7 +1740,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44725</v>
       </c>
       <c r="B25" t="n">
@@ -1781,7 +1793,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44732</v>
       </c>
       <c r="B26" t="n">
@@ -1834,7 +1846,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44739</v>
       </c>
       <c r="B27" t="n">
@@ -1887,7 +1899,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44746</v>
       </c>
       <c r="B28" t="n">
@@ -1940,7 +1952,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44753</v>
       </c>
       <c r="B29" t="n">
@@ -1993,7 +2005,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44760</v>
       </c>
       <c r="B30" t="n">
@@ -2046,7 +2058,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44767</v>
       </c>
       <c r="B31" t="n">
@@ -2099,7 +2111,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B32" t="n">
@@ -2152,7 +2164,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44781</v>
       </c>
       <c r="B33" t="n">
@@ -2205,7 +2217,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44788</v>
       </c>
       <c r="B34" t="n">
@@ -2258,7 +2270,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44795</v>
       </c>
       <c r="B35" t="n">
@@ -2311,7 +2323,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44802</v>
       </c>
       <c r="B36" t="n">
@@ -2364,7 +2376,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44809</v>
       </c>
       <c r="B37" t="n">
@@ -2417,7 +2429,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44816</v>
       </c>
       <c r="B38" t="n">
@@ -2470,7 +2482,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44823</v>
       </c>
       <c r="B39" t="n">
@@ -2523,7 +2535,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44830</v>
       </c>
       <c r="B40" t="n">
@@ -2576,7 +2588,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44837</v>
       </c>
       <c r="B41" t="n">
@@ -2629,7 +2641,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44844</v>
       </c>
       <c r="B42" t="n">
@@ -2682,7 +2694,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44851</v>
       </c>
       <c r="B43" t="n">
@@ -2735,7 +2747,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44858</v>
       </c>
       <c r="B44" t="n">
@@ -2788,7 +2800,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B45" t="n">
@@ -2841,7 +2853,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44872</v>
       </c>
       <c r="B46" t="n">
@@ -2894,7 +2906,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44879</v>
       </c>
       <c r="B47" t="n">
@@ -2947,7 +2959,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44886</v>
       </c>
       <c r="B48" t="n">
@@ -3000,7 +3012,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44893</v>
       </c>
       <c r="B49" t="n">
@@ -3053,7 +3065,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44900</v>
       </c>
       <c r="B50" t="n">
@@ -3106,7 +3118,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44907</v>
       </c>
       <c r="B51" t="n">
@@ -3159,7 +3171,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44914</v>
       </c>
       <c r="B52" t="n">
@@ -3212,7 +3224,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44921</v>
       </c>
       <c r="B53" t="n">
@@ -3265,7 +3277,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44928</v>
       </c>
       <c r="B54" t="n">
@@ -3318,7 +3330,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44935</v>
       </c>
       <c r="B55" t="n">
@@ -3371,7 +3383,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44942</v>
       </c>
       <c r="B56" t="n">
@@ -3424,7 +3436,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44949</v>
       </c>
       <c r="B57" t="n">
@@ -3477,7 +3489,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44956</v>
       </c>
       <c r="B58" t="n">
@@ -3530,7 +3542,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44963</v>
       </c>
       <c r="B59" t="n">
@@ -3583,7 +3595,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="B60" t="n">
@@ -3636,7 +3648,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44977</v>
       </c>
       <c r="B61" t="n">
@@ -3689,7 +3701,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="B62" t="n">
@@ -3742,7 +3754,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44991</v>
       </c>
       <c r="B63" t="n">
@@ -3795,7 +3807,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44998</v>
       </c>
       <c r="B64" t="n">
@@ -3848,7 +3860,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45005</v>
       </c>
       <c r="B65" t="n">
@@ -3901,7 +3913,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45012</v>
       </c>
       <c r="B66" t="n">
@@ -3954,7 +3966,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45019</v>
       </c>
       <c r="B67" t="n">
@@ -4007,7 +4019,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45026</v>
       </c>
       <c r="B68" t="n">
@@ -4060,7 +4072,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45033</v>
       </c>
       <c r="B69" t="n">
@@ -4113,7 +4125,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45040</v>
       </c>
       <c r="B70" t="n">
@@ -4166,7 +4178,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B71" t="n">
@@ -4219,7 +4231,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="B72" t="n">
@@ -4272,7 +4284,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45061</v>
       </c>
       <c r="B73" t="n">
@@ -4325,7 +4337,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45068</v>
       </c>
       <c r="B74" t="n">
@@ -4378,7 +4390,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45075</v>
       </c>
       <c r="B75" t="n">
@@ -4431,7 +4443,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45082</v>
       </c>
       <c r="B76" t="n">
@@ -4484,7 +4496,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45089</v>
       </c>
       <c r="B77" t="n">
@@ -4537,7 +4549,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45096</v>
       </c>
       <c r="B78" t="n">
@@ -4590,7 +4602,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="B79" t="n">
@@ -4643,7 +4655,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45110</v>
       </c>
       <c r="B80" t="n">
@@ -4696,7 +4708,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45117</v>
       </c>
       <c r="B81" t="n">
@@ -4749,7 +4761,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45124</v>
       </c>
       <c r="B82" t="n">
@@ -4802,7 +4814,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="B83" t="n">
@@ -4855,7 +4867,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B84" t="n">
@@ -4908,7 +4920,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="B85" t="n">
@@ -4961,7 +4973,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45152</v>
       </c>
       <c r="B86" t="n">
@@ -5014,7 +5026,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45159</v>
       </c>
       <c r="B87" t="n">
@@ -5067,7 +5079,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45166</v>
       </c>
       <c r="B88" t="n">
@@ -5120,7 +5132,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45173</v>
       </c>
       <c r="B89" t="n">
@@ -5173,7 +5185,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45180</v>
       </c>
       <c r="B90" t="n">
@@ -5226,7 +5238,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45187</v>
       </c>
       <c r="B91" t="n">
@@ -5279,7 +5291,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45194</v>
       </c>
       <c r="B92" t="n">
@@ -5332,7 +5344,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45201</v>
       </c>
       <c r="B93" t="n">
@@ -5385,7 +5397,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45208</v>
       </c>
       <c r="B94" t="n">
@@ -5438,7 +5450,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45215</v>
       </c>
       <c r="B95" t="n">
@@ -5491,7 +5503,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45222</v>
       </c>
       <c r="B96" t="n">
@@ -5544,7 +5556,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45229</v>
       </c>
       <c r="B97" t="n">
@@ -5597,7 +5609,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45236</v>
       </c>
       <c r="B98" t="n">
@@ -5650,7 +5662,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45243</v>
       </c>
       <c r="B99" t="n">
@@ -5703,7 +5715,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45250</v>
       </c>
       <c r="B100" t="n">
@@ -5756,7 +5768,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45257</v>
       </c>
       <c r="B101" t="n">
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45264</v>
       </c>
       <c r="B102" t="n">
@@ -5862,7 +5874,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45271</v>
       </c>
       <c r="B103" t="n">
@@ -5915,7 +5927,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45278</v>
       </c>
       <c r="B104" t="n">
@@ -5968,7 +5980,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45285</v>
       </c>
       <c r="B105" t="n">
@@ -6021,7 +6033,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B106" t="n">
@@ -6074,7 +6086,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45299</v>
       </c>
       <c r="B107" t="n">
@@ -6127,7 +6139,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45306</v>
       </c>
       <c r="B108" t="n">
@@ -6180,7 +6192,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45313</v>
       </c>
       <c r="B109" t="n">
@@ -6233,7 +6245,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45320</v>
       </c>
       <c r="B110" t="n">
@@ -6286,7 +6298,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="B111" t="n">
@@ -6339,7 +6351,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="B112" t="n">
@@ -6392,7 +6404,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45341</v>
       </c>
       <c r="B113" t="n">
@@ -6445,7 +6457,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="B114" t="n">
@@ -6498,7 +6510,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45355</v>
       </c>
       <c r="B115" t="n">
@@ -6551,7 +6563,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45362</v>
       </c>
       <c r="B116" t="n">
@@ -6604,7 +6616,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45369</v>
       </c>
       <c r="B117" t="n">
@@ -6657,7 +6669,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="B118" t="n">
@@ -6710,7 +6722,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B119" t="n">
@@ -6763,7 +6775,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45390</v>
       </c>
       <c r="B120" t="n">
@@ -6816,7 +6828,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45397</v>
       </c>
       <c r="B121" t="n">
@@ -6869,7 +6881,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45404</v>
       </c>
       <c r="B122" t="n">
@@ -6922,7 +6934,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45411</v>
       </c>
       <c r="B123" t="n">
@@ -6975,7 +6987,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="B124" t="n">
@@ -7028,7 +7040,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45425</v>
       </c>
       <c r="B125" t="n">
@@ -7081,7 +7093,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45432</v>
       </c>
       <c r="B126" t="n">
@@ -7134,7 +7146,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45439</v>
       </c>
       <c r="B127" t="n">
@@ -7187,7 +7199,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45446</v>
       </c>
       <c r="B128" t="n">
@@ -7240,7 +7252,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45453</v>
       </c>
       <c r="B129" t="n">
@@ -7293,7 +7305,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B130" t="n">
@@ -7346,7 +7358,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B131" t="n">
@@ -7399,7 +7411,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B132" t="n">
@@ -7452,7 +7464,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B133" t="n">
@@ -7505,7 +7517,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="B134" t="n">
@@ -7558,7 +7570,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45495</v>
       </c>
       <c r="B135" t="n">
@@ -7611,7 +7623,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="B136" t="n">
@@ -7664,7 +7676,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="B137" t="n">
@@ -7717,7 +7729,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45516</v>
       </c>
       <c r="B138" t="n">
@@ -7770,7 +7782,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45523</v>
       </c>
       <c r="B139" t="n">
@@ -7823,7 +7835,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45530</v>
       </c>
       <c r="B140" t="n">
@@ -7876,7 +7888,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45537</v>
       </c>
       <c r="B141" t="n">
@@ -7929,7 +7941,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B142" t="n">
@@ -7982,7 +7994,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45551</v>
       </c>
       <c r="B143" t="n">
@@ -8035,7 +8047,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B144" t="n">
@@ -8088,7 +8100,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B145" t="n">
@@ -8141,7 +8153,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="B146" t="n">
@@ -8194,7 +8206,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45579</v>
       </c>
       <c r="B147" t="n">
@@ -8247,7 +8259,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B148" t="n">
@@ -8300,7 +8312,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45593</v>
       </c>
       <c r="B149" t="n">
@@ -8353,7 +8365,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="B150" t="n">
@@ -8406,7 +8418,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45607</v>
       </c>
       <c r="B151" t="n">
@@ -8459,7 +8471,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45614</v>
       </c>
       <c r="B152" t="n">
@@ -8512,7 +8524,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45621</v>
       </c>
       <c r="B153" t="n">
@@ -8565,7 +8577,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45628</v>
       </c>
       <c r="B154" t="n">
@@ -8618,7 +8630,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45635</v>
       </c>
       <c r="B155" t="n">
@@ -8671,7 +8683,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45642</v>
       </c>
       <c r="B156" t="n">
@@ -8724,7 +8736,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45649</v>
       </c>
       <c r="B157" t="n">
@@ -8777,7 +8789,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45656</v>
       </c>
       <c r="B158" t="n">
@@ -8830,7 +8842,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45663</v>
       </c>
       <c r="B159" t="n">
@@ -8883,7 +8895,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="B160" t="n">
@@ -8936,7 +8948,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45677</v>
       </c>
       <c r="B161" t="n">
@@ -8989,7 +9001,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="B162" t="n">
@@ -9042,7 +9054,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45691</v>
       </c>
       <c r="B163" t="n">
@@ -9095,7 +9107,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="B164" t="n">
@@ -9148,7 +9160,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45705</v>
       </c>
       <c r="B165" t="n">
@@ -9201,7 +9213,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="B166" t="n">
@@ -9254,7 +9266,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45719</v>
       </c>
       <c r="B167" t="n">
@@ -9307,7 +9319,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="B168" t="n">
@@ -9360,7 +9372,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45733</v>
       </c>
       <c r="B169" t="n">
@@ -9413,7 +9425,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="B170" t="n">
@@ -9466,7 +9478,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B171" t="n">
@@ -9519,7 +9531,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45754</v>
       </c>
       <c r="B172" t="n">
@@ -9572,7 +9584,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="B173" t="n">
@@ -9625,7 +9637,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45768</v>
       </c>
       <c r="B174" t="n">
@@ -9678,7 +9690,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="B175" t="n">
@@ -9731,7 +9743,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="B176" t="n">
@@ -9784,7 +9796,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="B177" t="n">
@@ -9837,7 +9849,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45796</v>
       </c>
       <c r="B178" t="n">
@@ -9890,7 +9902,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="B179" t="n">
@@ -9943,7 +9955,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45810</v>
       </c>
       <c r="B180" t="n">
@@ -9996,7 +10008,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="B181" t="n">
@@ -10049,7 +10061,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45824</v>
       </c>
       <c r="B182" t="n">
@@ -10102,7 +10114,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="B183" t="n">
@@ -10155,7 +10167,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B184" t="n">
@@ -10208,7 +10220,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45845</v>
       </c>
       <c r="B185" t="n">
@@ -10261,7 +10273,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="B186" t="n">
@@ -10314,7 +10326,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="B187" t="n">
@@ -10367,7 +10379,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="B188" t="n">
@@ -10420,7 +10432,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="B189" t="n">
@@ -10473,7 +10485,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="B190" t="n">
@@ -10526,7 +10538,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45887</v>
       </c>
       <c r="B191" t="n">
@@ -10579,7 +10591,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="B192" t="n">
@@ -10632,7 +10644,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B193" t="n">
@@ -10685,7 +10697,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="B194" t="n">
@@ -10738,7 +10750,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45915</v>
       </c>
       <c r="B195" t="n">
@@ -10791,7 +10803,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="B196" t="n">
@@ -10844,7 +10856,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45929</v>
       </c>
       <c r="B197" t="n">
@@ -10897,7 +10909,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45936</v>
       </c>
       <c r="B198" t="n">
@@ -10950,7 +10962,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="B199" t="n">
@@ -11003,7 +11015,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45950</v>
       </c>
       <c r="B200" t="n">
@@ -11056,7 +11068,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="B201" t="n">
@@ -11109,7 +11121,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="B202" t="n">
@@ -11162,7 +11174,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="B203" t="n">
@@ -11215,7 +11227,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45978</v>
       </c>
       <c r="B204" t="n">
@@ -11268,7 +11280,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="B205" t="n">
@@ -11321,7 +11333,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B206" t="n">
@@ -11374,7 +11386,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="B207" t="n">
@@ -11427,7 +11439,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>46006</v>
       </c>
       <c r="B208" t="n">
@@ -11480,7 +11492,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="B209" t="n">
@@ -11533,7 +11545,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>46020</v>
       </c>
       <c r="B210" t="n">
@@ -11586,7 +11598,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>46027</v>
       </c>
       <c r="B211" t="n">
@@ -11639,7 +11651,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>46034</v>
       </c>
       <c r="B212" t="n">
@@ -11692,7 +11704,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>46041</v>
       </c>
       <c r="B213" t="n">
@@ -11745,7 +11757,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>46048</v>
       </c>
       <c r="B214" t="n">
@@ -11798,7 +11810,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>46055</v>
       </c>
       <c r="B215" t="n">
@@ -11851,7 +11863,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="B216" t="n">
@@ -11904,7 +11916,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>46069</v>
       </c>
       <c r="B217" t="n">
@@ -11957,7 +11969,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="B218" t="n">
@@ -12010,7 +12022,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="B219" t="n">
@@ -12063,7 +12075,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>46090</v>
       </c>
       <c r="B220" t="n">
@@ -12116,7 +12128,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="B221" t="n">
@@ -12169,7 +12181,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>46104</v>
       </c>
       <c r="B222" t="n">
@@ -12222,7 +12234,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="B223" t="n">
@@ -12275,7 +12287,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="B224" t="n">
@@ -12328,7 +12340,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="B225" t="n">
@@ -12381,7 +12393,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>46132</v>
       </c>
       <c r="B226" t="n">
@@ -12434,7 +12446,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="B227" t="n">
@@ -12487,7 +12499,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="B228" t="n">
@@ -12540,7 +12552,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="B229" t="n">
@@ -12593,7 +12605,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>46160</v>
       </c>
       <c r="B230" t="n">
@@ -12646,7 +12658,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="B231" t="n">
@@ -12713,12 +12725,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
